--- a/Manual Idea Bank/paper_opinions_database.xlsx
+++ b/Manual Idea Bank/paper_opinions_database.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasroever/Dropbox/Promotion/IDEAS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nicolasroever/Dropbox/Promotion/IDEAS/Manual Idea Bank/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{472817A7-0D06-404F-A2A9-E7E231E27D06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A152643-3ABD-1546-89E7-F100DE0FE7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="500" windowWidth="25240" windowHeight="27540" xr2:uid="{7D8FD4A0-F6F0-1648-95D8-71024BE4EA6B}"/>
+    <workbookView xWindow="360" yWindow="500" windowWidth="34120" windowHeight="27540" xr2:uid="{7D8FD4A0-F6F0-1648-95D8-71024BE4EA6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t>Title</t>
   </si>
@@ -346,6 +346,239 @@
   </si>
   <si>
     <t>MAJOR ISSUES: (1) Survey experiment lacks a clear hypothesis - sits between information processing, policy prediction, and financial asset valuation without addressing any in detail. Cannot distinguish whether participants' wrong predictions are due to wrong policy beliefs or wrong understanding of stock markets. (5) Contribution not nearly significant enough for Top-5. Recommend REJECT.</t>
+  </si>
+  <si>
+    <t>Tacit Knowledge Markets: How Research Taste Propagates Through Advisor-Student Networks and Shapes Field Evolution</t>
+  </si>
+  <si>
+    <t>"Can we measure the \"tacit\" component of research taste\u2014the part that isn't explained by topic, method, or co-authorship\u2014and show that it propagates through advisor-student links with predictable decay, shaping which research programs thrive or die?",
+    "insight": "Economists act on research taste they cannot articulate (Polanyi's tacit knowledge), yet we model science as if ideas compete on merit alone. The key move is to use LLM embeddings of paper abstracts to construct a \"style\" residual after removing topic and method, then show this residual is heritable through advising chains. This would be the first empirical measurement of tacit knowledge transmission in any professional setting.",
+    "empirical_data": "Use the full NBER working paper corpus + ProQuest dissertation data to link advisor-advisee pairs; compute semantic embeddings (e.g., from GPT-4) of abstracts, regress on topic fixed effects and method indicators, then test whether the residual \"style vector\" correlates within advisor lineages using a gravity-style model with genealogical distance.\n\n---"</t>
+  </si>
+  <si>
+    <t>- This is interesting, because it uses a novel method to get at something real
+- I am not sure what to do with such a result, however it could be informative of inequality and show proof how hard it is for outsiders to get into an elite circle
+- I kind of do not like that this is only in the research space, I sometimes do not like research studying research, because it feels like this is not soo externally valid
+- But ok idea</t>
+  </si>
+  <si>
+    <t>Product Market Traps in Education: Do Students Stay in Prestigious Programs They'd Prefer Not to Exist?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "question": "Analogous to the Allcott et al. TikTok/Instagram collective trap, do students enrolled in elite-but-miserable degree programs (law, MBA, medicine) exhibit negative welfare when accounting for the externality that others' enrollment forces them to participate?",
+    "insight": "The \"collective trap\" framework from social media applies naturally to positional goods in education\u2014where the value of not having a credential is endogenous to how many peers hold one. The surprising prediction is that students in the most prestigious programs may have the most negative adjusted welfare, because the positional externality is strongest precisely where the credential is most valuable. This reframes the \"rat race\" as a measurable market failure.",
+    "empirical_data": "Run incentivized WTA/WTP experiments with students at a partner university (e.g., through PumpkinCareers' student consulting network) measuring: (a) private valuation of their own enrollment, (b) WTP for a world where the program doesn't exist for anyone, yielding Allcott-style adjusted surplus measures across programs.\n\n---"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- I really like the application and it is super relevant! 
+- The conceptual contribution here however seems a bit marginal 
+</t>
+  </si>
+  <si>
+    <t>Preference Laundering Through Algorithms: How People Use Recommendation Systems to Consume Content They Cannot Admit Wanting</t>
+  </si>
+  <si>
+    <t>**Question:** Do consumers strategically manipulate their algorithmic profiles to receive recommendations for content they desire but find socially or personally unacceptable to actively seek, and does this "preference laundering" increase welfare?
+**Key insight:** This connects to the idea of preferences people cannot admit to themselves (like closeted sexuality). Algorithmic recommendations create a psychologically distinct consumption pathway—"the algorithm showed me this" provides plausible deniability both socially and to oneself. This means recommendation algorithms serve a function that existing models completely miss: they are commitment devices for consuming taboo-adjacent goods. This reframes the "filter bubble" debate entirely.
+**Identification:** Design an experiment on a content platform where users are randomized into (a) active search only, (b) algorithmic feed only, or (c) both, measuring consumption of pre-categorized sensitive content (political out-group media, mental health content, gender-atypical content) and post-consumption self-reports of satisfaction and attribution ("I chose this" vs. "it was recommended").</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- It is a smart idea, saying that people want "plausible deniability" and actively seek mechanisms that provide it
+- I am not yet convinced by the identifiation strategy, so this is not yet there. It is a clever start, not more </t>
+  </si>
+  <si>
+    <t>When the Market Discovers Your Secret: The Welfare Effects of Algorithmic Outing in Insurance Markets</t>
+  </si>
+  <si>
+    <t>**Question:** Does the increasing ability of insurers to predict previously unobservable risk types (via wearables, genetic data, digital footprints) improve or destroy welfare, and does the answer depend on whether the insured *themselves* knew their type?
+**Key insight:** Classical adverse selection (Akerlof) assumes agents know their own type—but what if people are in denial or genuinely ignorant about their health risks, and algorithms reveal this? The welfare calculus flips: information revelation may cause psychological harm (forced self-knowledge) even as it solves adverse selection. For people who strategically avoid health information (as documented in the "ostrich effect" literature), algorithmic typing constitutes a form of involuntary outing analogous to revealing sexual orientation. Markets can "work" in the efficiency sense while making participants worse off.
+**Identification:** Use a large insurer's introduction of wearable-based premium discounts as a natural experiment. Compare take-up, subsequent health-seeking behavior, and mental health claims between enrollees who receive "surprising" risk feedback (predicted risk diverges from self-assessed risk, measured pre-enrollment) vs. those whose predictions confirm self-assessments.</t>
+  </si>
+  <si>
+    <t>- the question itself is extremely smart-what happens when the infomration assymetry in insurance market flips around
+- the identification is hard, but this is an amazing direction</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Confessing to the Algorithm: Do People Reveal Stigmatized Preferences More Honestly to AI Than to Human Surveyors?</t>
+  </si>
+  <si>
+    <t>**Question:** Does replacing a human interviewer with an AI chatbot in sensitive survey contexts (sexual orientation, drug use, political extremism) reduce social desirability bias, and does this effect vary with respondents' beliefs about AI's capacity for judgment?
+**Key insight:** Survey methodology has long struggled with social desirability bias; list experiments and RRT are partial fixes. The non-obvious insight is that AI interviewers might function as a "judgment-free" elicitation device—but only if respondents don't anthropomorphize the AI. This creates a testable interaction: the bias-reduction effect of AI should be largest for people who score lowest on AI anthropomorphism, completely inverting the naive prediction that people who "trust" AI more would reveal more.
+**Identification:** Run a between-subjects field experiment via Bloit Inc.'s AI-psychotherapy platform (or similar) randomizing whether sensitive intake questions are asked by a human therapist, an AI with humanlike avatar, or a clearly-labeled minimal AI interface; measure disclosure rates against validated benchmarks (e.g., known population base rates for substance use from biomarker studies).</t>
+  </si>
+  <si>
+    <t>- I think this idea is nice. AI interviewers can plausibly overcome biases in surveys we previouslty had. But the human comparison is off in my view, AI interviewers are more comapred with standard online surveys</t>
+  </si>
+  <si>
+    <t>Outside Options You Can't Take: How Phantom Alternatives Inflate Bargaining Power in Gig Platforms</t>
+  </si>
+  <si>
+    <t>**Question:** Do gig economy platforms (Uber, DoorDash) strategically display earnings information from alternative gigs that workers cannot practically access—creating "phantom outside options" that paradoxically increase workers' subjective continuation value and reduce quit rates?
+**Key insight:** Standard bargaining theory (as in the Hwang paper) treats outside options as real. But platforms may exploit a behavioral wedge: showing workers that "drivers in your area earn $X on Platform Y" makes workers feel they have options, increasing their sense of control and reducing actual search—the opposite of what a rational model predicts. This is a novel form of "choice architecture as labor discipline" that inverts the classical role of outside options.
+**Identification:** Collect screenshots of in-app notifications from gig workers (via a browser extension/survey panel of ~500 gig workers), link to GPS-based labor supply data and actual platform-switching behavior; exploit variation across cities in the availability of competing platforms to test whether "phantom" information (competitor info when no real competitor exists locally) reduces churn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- it is super interesting to think about this. Because we think a lot about real outside options and know they have a large impact - and noone has ever looked at fake outside options. Here we could see the difference between psychological and real effects. 
+- I am not entirely convinced by the empirical strategy, getting this data seems hard. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dead Drugs Walking: How Patients' Causal Models of Their Own Illness Predict Medication Non-Adherence Better Than Price</t>
+  </si>
+  <si>
+    <t>**Question:** Do patients' folk causal models of disease mechanisms (e.g., "my body builds tolerance" or "I only need medication when symptomatic") explain more variance in drug non-adherence than out-of-pocket costs, even among those facing the Medicare Part D coverage gap?
+**Key insight:** The Einav et al. "Health Costs of Cost Sharing" paper shows cost-sharing kills—but the finding that only one-third of patients believe missing drugs for a month matters suggests the binding constraint may not be price but causal beliefs. If patients' mental models of pharmacology are the first-order problem, then the optimal policy is information design, not subsidy design. This reframes a classic market failure (moral hazard/cost-sharing) as fundamentally an epistemic failure.
+**Identification:** Augment CMS Medicare Part D claims data with a survey measuring patients' causal models of their specific conditions (elicited via causal diagram tasks), then estimate heterogeneous treatment effects of the coverage gap on adherence/mortality as a function of causal model accuracy.</t>
+  </si>
+  <si>
+    <t>- I think this takes a very insightful idea about human nature: We are proud folks, and have very strong opinions about our health and bodies
+- Now, thinking about how this interferes with more conventional market forces is fascinating. 
+- But I am not fully convinced by the empirical strategy, Medicare data seems hard to get</t>
+  </si>
+  <si>
+    <t>The Unraveling of Anonymous Peer Review: How AI Detection Accusations Create a New Lemons Problem in Academic Publishing</t>
+  </si>
+  <si>
+    <t>**Question:** Does the suspicion that submitted papers may be AI-generated cause reviewers to systematically penalize well-written papers by unknown authors, creating an adverse selection dynamic that favors established researchers?
+**Key insight:** Akerlof's lemons logic applies in reverse: when quality signals (clear prose, comprehensive literature reviews) become associated with AI use, the market for ideas penalizes exactly the papers that look "too good" from newcomers. This generates a perverse equilibrium where junior researchers strategically write worse to signal authenticity, while established researchers face no such penalty due to reputation capital. This is a novel information asymmetry created by technology.
+**Identification:** Submit pairs of identical papers (varying only author reputation signals: unknown vs. established-sounding affiliations) to a simulated peer review exercise with ~500 active reviewers recruited via Prolific, randomizing whether papers include a disclaimer about AI non-use, and measuring review scores and explicit AI suspicion flags.</t>
+  </si>
+  <si>
+    <t>- I am not a super huge fan of research on research, because it feels like we are completely staying in our bubble, so we need to have some ideas of external validity here
+– With AI, there is a lot more going on; the reviewer side also uses AI, so this only seems to tell one part of a story with important parts missing</t>
+  </si>
+  <si>
+    <t>The Price of Performing Poverty: How Means-Testing Bureaucracy Functions as a Signaling Game That Selects Against the Working Poor</t>
+  </si>
+  <si>
+    <t>**Question:** Does the administrative burden of means-tested programs (documentation, wait times, repeated verification) function as a separating equilibrium that screens out precisely those low-income individuals with the highest opportunity cost of time—namely, the self-employed and gig workers?
+**Key insight:** Existing work frames administrative burden as a cost; the reframing here is that it's an inadvertent auction mechanism that allocates benefits based on willingness-to-wait rather than need. Combined with the Hamory et al. insight that the self-employed's time is poorly valued, this means current welfare systems are systematically biased against the informally employed. This is a market design failure hiding inside bureaucratic design.
+**Identification:** Use India's Bhamashah program (as in Dupas et al.) or a comparable means-tested program with administrative data on application attempts, completion rates, and time-to-enrollment, linked to occupational data. Exploit variation in local office processing times (e.g., staff shortages) as an instrument for administrative burden.</t>
+  </si>
+  <si>
+    <t>- I think this is rather obvious: Wait-times are costly, and administrative burden is hard for those who are not well-educated or short on time
+- I think framing this as a market problem is a big stretch. It is more heterogenous costs</t>
+  </si>
+  <si>
+    <t>The Lemons Problem in AI Therapy: How Unobservable Quality Drives Out Human Therapists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Does the entry of AI therapy tools (like Bloit Inc.'s AI-psychotherapy) create an adverse selection spiral where high-quality human therapists exit the market because consumers cannot distinguish quality, while low-quality human therapists remain to compete on price with AI?",
+    "insight": "Akerlof's lemons mechanism has never been studied in a credentialing-heavy service market undergoing sudden technological disruption. The non-obvious part: AI doesn't just substitute for low-quality providers\u2014it destroys the signaling equilibrium that previously separated good from bad therapists, because AI compresses the perceived quality distribution. Consumers who can't tell good from bad therapy default to cheap AI, pushing out the best human therapists first (who have the highest outside options).",
+    "empirical_data": "Scrape therapist directories (Psychology Today, BetterHelp) longitudinally to track entry/exit of therapists by credentials and reviews, combined with state-level variation in AI therapy regulation; supplement with a discrete choice experiment on Prolific measuring willingness-to-pay for therapy as a function of AI disclosure and therapist signals.\n\n---"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- This is just not true. Because there is an AI, people might be even better at discerning the really bad therapists (because they are clearly worse than the AI)
+- Also, the AI might be even the best choice for many
+- This is a research idea which does not make logical sense
+</t>
+  </si>
+  <si>
+    <t>The Causal Model Discount: Do Consumers Who Understand Why a Product Works Pay Less for Signaling Substitutes?</t>
+  </si>
+  <si>
+    <t>"question": "When consumers acquire a correct causal model of why a product works (e.g., vitamins, skincare, organic food), do they substitute toward cheaper functional equivalents, and does this compress brand premia\u2014revealing that ignorance of mechanism is what sustains premium pricing?",
+    "insight": "Standard information economics focuses on quality uncertainty, but there's a deeper layer: uncertainty about *why* something works. A consumer who doesn't understand the mechanism behind \"organic\" or \"probiotic\" must rely on brand as a heuristic, paying a premium. Once the causal model is supplied, the brand premium should collapse\u2014but only for products where the mechanism is simple enough to internalize. This predicts heterogeneous effects by product complexity, which distinguishes it from standard disclosure results.",
+    "empirical_data": "Pre-register a large online experiment (N=3,000+) where participants receive mechanistic explanations (vs. placebo information) about product categories varying in causal complexity (Vitamin C vs. probiotic gut health vs. organic produce), then make incentivized purchase decisions from real product listings; measure brand premium compression.\n\n---"</t>
+  </si>
+  <si>
+    <t>- My first instinct is that this is interesting. But I mean it is just a standard information result (if you understand you understand that the premium is worthless)
+- As a start this could work, as we then continue thinking about inequality in markets with information asymmetry? It opens something in my head, but this is not there yet</t>
+  </si>
+  <si>
+    <t>The Dunning-Kruger Market: How Overconfident Sellers Sustain High-Quality Equilibria in Expert Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Does seller overconfidence about their own quality paradoxically prevent market unraveling in credence goods markets (legal services, consulting, therapy), by keeping high-quality providers in the market who would otherwise exit if they correctly estimated their returns?",
+    "insight": "In a standard lemons model, high-quality sellers exit because the market doesn't reward quality. But if high-quality providers systematically overestimate how much the market recognizes their quality (a well-documented bias among experts), they stay in the market \"too long,\" inadvertently sustaining average quality. This means a cognitive bias\u2014normally seen as a market friction\u2014actually functions as the glue holding credence goods markets together. Correcting overconfidence (e.g., through transparent rating systems) could paradoxically cause market unraveling.",
+    "empirical_data": "Survey ~1,000 providers on a freelance platform (Upwork or similar) measuring their beliefs about own quality ranking and expected future earnings, then link to actual platform ratings, earnings trajectories, and exit decisions over 18 months. Exploit the staggered rollout of enhanced analytics dashboards (which give providers clearer signals about their relative standing) as a natural experiment that \"corrects\" overconfidence."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- I like this, because it flips the standard logic of Akerlof the other way around - and it is plausible
+- These information provision experiments are cheap, but somehow a bit overdone by now I think. </t>
+  </si>
+  <si>
+    <t>The Price of Silence: How Anonymous Grading Policies Reveal Gender and Ethnic Bias in University Economics Departments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "question": "Does the staggered adoption of anonymous grading policies across university departments causally reveal the magnitude of identity-based grading bias, and does this bias predict subsequent career sorting out of economics?",
+    "insight": "Most studies of grading bias compare across institutions or use lab experiments. The key move here is exploiting the fact that many universities adopted anonymous grading at the department level at different times (and some departments within the same university still haven't), creating a staggered diff-in-diff where the same student is graded anonymously in some courses and non-anonymously in others within the same semester. This within-student variation eliminates selection concerns entirely. The deeper contribution is linking the revealed bias magnitude to downstream career outcomes\u2014showing that grading bias is a mechanism for talent misallocation in economics itself.",
+    "empirical_data": "Partner with 3-5 UK universities (where anonymous marking has been adopted heterogeneously across departments since ~2005) to obtain transcript-level data with student fixed effects, linking to HESA Destinations of Leavers surveys for career outcomes.\n\n---"</t>
+  </si>
+  <si>
+    <t>- I think this is a case were there is absolutely no conceptual depth; it is mere datacrunching
+– I would not like to do a project where the main insight is one number; we already know discrimination exists and that anonymous grading is good, now estimating the magnitude is not a super clever research project</t>
+  </si>
+  <si>
+    <t>The Invisible Curriculum: How Random Teacher-Student Dialect Matching Affects Human Capital Formation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Does the quasi-random assignment of students to teachers who share their regional dialect causally improve academic performance, and is this effect mediated by altered expectations, communication clarity, or identity-based trust?",
+    "insight": "A large literature studies teacher-student racial and gender matching, but dialect is a richer and more continuous source of in-group/out-group identification that operates below conscious awareness\u2014connecting to the paper's interest in tacit knowledge. The identification uses the fact that in centralized teacher assignment systems (e.g., France's *mouvement*, Italy's transfer system), teachers are assigned to schools based on seniority points and slot availability, generating quasi-random variation in dialect distance between teacher and students within the same region. The mechanism decomposition matters: if it's trust/identity rather than comprehension, this suggests market failures in education extend beyond information to social-norm-mediated engagement.\n\nINSIGHT (continued): Dialect distance can be continuously measured using NLP on regional speech corpora, creating a dose-response design rather than a binary match indicator.",
+    "empirical_data": "Italian INVALSI student test score data linked to teacher assignment records from the Ministry of Education, combined with computational dialect-distance measures from the ALT (Atlante Linguistico della Toscana) or AIS dialect atlas, exploiting the centralized transfer system as an instrument.\n\n---</t>
+  </si>
+  <si>
+    <t>Hard to think of a more irrelevant question than this</t>
+  </si>
+  <si>
+    <t>The Lemons Problem in AI-Generated Research: Quality Uncertainty When Reviewers Cannot Distinguish Human from Machine Scholarship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Does the inability of peer reviewers to distinguish AI-assisted from human-generated research create an Akerlof lemons dynamic that drives high-effort human researchers out of certain subfields?",
+    "insight": "Akerlof's insight was about *statistical* quality discrimination\u2014buyers evaluate based on group averages. As AI lowers the cost of producing mediocre-but-polished manuscripts, reviewers cannot price quality at the individual level, so returns to genuine intellectual effort fall toward the group mean. This is the first application of the lemons model to the knowledge production market itself, which is striking because academia's entire institutional apparatus (peer review, tenure) exists precisely to solve this problem and may be failing.",
+    "empirical_data": "Conduct a large-scale experiment submitting pairs of abstracts/short papers to economists and other researchers for evaluation\u2014one human-written, one AI-generated on identical topics\u2014measuring detection accuracy, quality ratings, and stated willingness-to-cite, combined with a survey of researchers' own AI use and perceived incentives to invest in deep thinking.\n\n---"</t>
+  </si>
+  <si>
+    <t>- I think this opens up something. A lot of our processes are designed to catch human errors, but now a lot of the stuff is done by AI
+- Also, thinking is outsourced more and more
+- So it is quite plausible that different discrimination patterns might emerge; with consequences for inequality</t>
+  </si>
+  <si>
+    <t>Markets Don't Clear Norms: Why the Law of One Price Fails When Transactions Carry Social Meaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Does the existence of social meaning attached to transactions (e.g., paying for sex, selling organs, charging friends for favors) create persistent, non-arbitrageable price distortions that violate the law of one price even in thick markets?",
+    "insight": "Economists generally treat \"repugnance\" as a friction that could in principle be overcome with enough surplus, but what if social meaning operates as an irreducible constraint\u2014not a transaction cost that shrinks with competition, but a force that *grows* with market thickness because observability increases? This would mean that some markets become *less* efficient as they scale, directly contradicting the standard intuition.",
+    "empirical_data": "Use cross-country variation in legalization of organ markets, sex work, and commercial surrogacy, combined with price and volume data from both legal and black markets. Supplement with vignette experiments varying market thickness (number of participants) and observability to test whether willingness to transact *decreases* as market size grows, conditional on social visibility.\n\n---"</t>
+  </si>
+  <si>
+    <t>- I like looking at stgmatized markets
+- I also love the focus on turning around a normally held belief and interacting it with social norms
+- Great idea!</t>
+  </si>
+  <si>
+    <t>The Efficiency of Inefficiency: Why Firms That Deliberately Waste Resources Outperform Optimizers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "Do firms that maintain organizational \"slack\"\u2014deliberately unoptimized budgets, redundant roles, unmonitored employee time\u2014systematically outperform firms that pursue allocative efficiency, and if so, does this challenge the fundamental assumption that competition selects for efficient firms?",
+    "insight": "Economics assumes competitive pressure drives firms toward the production possibility frontier, but if innovation, resilience, and employee creativity require *waste* (slack resources with no measurable ROI), then the most \"efficient\" firms are actually fragile and uncreative. The sacred cow is that market competition optimizes production\u2014but it may instead create a destructive race toward brittleness. This connects Google's famous \"20% time\" to a deeper theoretical point about the incompatibility of static efficiency and dynamic capability.",
+    "empirical_data": "Use the staggered adoption of private equity buyouts (which impose extreme efficiency optimization) as a natural experiment. Compare innovation output (patents, new products), survival rates during recessions, and long-run profitability of PE-targeted firms vs. matched controls using Compustat and patent data. Supplement with detailed time-use data from a partner firm (e.g., PumpkinCareers' consulting clients) measuring how employee \"unstructured\" time correlates with creative output.\n\n---"</t>
+  </si>
+  <si>
+    <t>- I like this, because it is a nice tradeoff between current and future returns
+- However I feel like this has been done before and is just a clever wording of stuff which has been done 1000 times</t>
+  </si>
+  <si>
+    <t>Information Doesn't Help: When Reducing Asymmetric Information Makes Markets Worse</t>
+  </si>
+  <si>
+    <t>"question": "Are there empirically important markets where providing more information to the less-informed party *reduces* total welfare by triggering adverse strategic responses from the more-informed party?",
+    "insight": "Since Akerlof, the profession has treated information asymmetry as a market failure that disclosure policies should fix. But if informed parties respond to disclosure requirements by strategically distorting the disclosed dimension (Goodharting), or if uninformed parties cannot process the information and instead use it as a signal of risk (\"why are they telling me this?\"), then mandatory disclosure can destroy the very markets it's meant to save. The sacred cow is that transparency is monotonically good.",
+    "empirical_data": "Study the staggered introduction of calorie labeling laws, clinical trial registrations, or Zillow's Zestimate across U.S. jurisdictions. Measure not just consumer behavior but *seller strategic response*\u2014do restaurants reformulate foods in unhealthy ways on undisclosed dimensions? Do home sellers delist when Zestimates are unfavorable, creating a new lemons problem? Use difference-in-differences with the precise rollout dates of these disclosure mandates.\n\n---"</t>
+  </si>
+  <si>
+    <t>- In theory, a great instinct
+- But idea is not yet enough borne out, some details are missing</t>
+  </si>
+  <si>
+    <t>he Willingness-to-Pay for Nothing: Experimental Evidence That WTP Measures Mostly Capture Survey Compliance, Not Preferences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "question": "What fraction of stated WTP in contingent valuation and incentive-compatible mechanisms reflects genuine economic preferences versus participants' desire to give the \"expected\" answer or simply complete the task?",
+    "insight": "WTP is the workhorse of welfare economics and cost-benefit analysis. But if a large share of measured WTP is an artifact of the elicitation process\u2014people anchoring on suggested prices, wanting to appear cooperative, or treating the task as a social interaction rather than an economic decision\u2014then trillions of dollars of policy decisions are based on noise. This isn't the usual \"hypothetical bias\" critique; the claim is that even *incentivized* mechanisms largely measure compliance with experimental demand rather than latent value.",
+    "empirical_data": "Design an experiment where participants state WTP for real goods *and* for fictitious goods (described with equal plausibility but literally nonexistent, revealed ex-post). If WTP for fictitious goods is substantial and correlated with WTP for real goods, this identifies the \"compliance\" component. Run on Prolific with N=5,000, varying experimenter authority cues, time pressure, and payment structure. Compare the compliance-adjusted WTP to market prices for the real goods.\n\n---"</t>
+  </si>
+  <si>
+    <t>- This is fascinating. From my own work, I have the instinct that WTP elicitations are tough and their external validity is not well understood so far</t>
   </si>
 </sst>
 </file>
@@ -402,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -412,6 +645,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -727,7 +969,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8FFAB25-B107-7B47-A76F-581BFCEE803F}">
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="65" style="1" customWidth="1"/>
@@ -739,7 +981,7 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -823,11 +1065,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="136" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="153" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1087,15 +1329,214 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
+    <row r="33" spans="1:3" ht="255" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="289" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="155" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="289" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="289" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="255" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="255" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="306" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="323" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="255" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="80" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="323" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="272" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="289" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
